--- a/Data/EXCEL/Transfer/salemon/202602/9943-salemon-202602.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202602/9943-salemon-202602.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDC67FD6-20DA-4AB9-A513-39534A2E17EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54DF507D-ABBA-446E-A108-3E25DE47EC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{4ADA8FBD-0108-43EF-BA79-0CA2F43AFA3E}"/>
+    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{BB637C7F-7D3E-4371-9523-27B529AC4045}"/>
   </bookViews>
   <sheets>
     <sheet name="9943-salemon-202602" sheetId="2" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1657229F-2623-4758-BFFA-F57E05A187EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DDBE3A-F2A6-48FE-A3C3-37BB7BCB0B34}">
   <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
